--- a/sources/bruce_step10.xlsx
+++ b/sources/bruce_step10.xlsx
@@ -821,6 +821,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>9b8fd4d4-3616-48c9-9abf-dc9f662f6010</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
           <t>9b8fd4d4-3616-48c9-9abf-dc9f662f6010</t>
@@ -888,6 +893,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>ee9855c7-2c2c-4519-b9a4-792540aae26a</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>ee9855c7-2c2c-4519-b9a4-792540aae26a</t>
@@ -953,6 +963,11 @@
       <c r="W7" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>b9d85c75-dc82-4368-83a4-ec8806a63d3b</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -9077,6 +9092,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2c1913ef-7e50-4413-a74d-b2910a2ebc07</t>
+        </is>
+      </c>
       <c r="AB95" t="inlineStr">
         <is>
           <t>2c1913ef-7e50-4413-a74d-b2910a2ebc07</t>
@@ -9134,6 +9154,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>0b8f5015-6736-4b0d-9890-9ab4d0f90726</t>
+        </is>
+      </c>
       <c r="AB96" t="inlineStr">
         <is>
           <t>0b8f5015-6736-4b0d-9890-9ab4d0f90726</t>
@@ -9196,6 +9221,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>1765f26e-c342-4b33-8701-d1a4207176f4</t>
+        </is>
+      </c>
       <c r="AB97" t="inlineStr">
         <is>
           <t>1765f26e-c342-4b33-8701-d1a4207176f4</t>
@@ -9263,6 +9293,11 @@
           <t>Use 1 to escape if the Left Knee Strike was done with 3, use 2 if the Left Knee Strike was done with 4.</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>b8fd9af3-2ecd-4885-ae0b-82af642e3380</t>
+        </is>
+      </c>
       <c r="AB98" t="inlineStr">
         <is>
           <t>b8fd9af3-2ecd-4885-ae0b-82af642e3380</t>
@@ -9323,6 +9358,11 @@
       <c r="W99" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>3cdc0ff6-007b-40aa-b73f-e08284f85ced</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">

--- a/sources/bruce_step10.xlsx
+++ b/sources/bruce_step10.xlsx
@@ -417,39 +417,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD102"/>
+  <dimension ref="A1:AE102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col hidden="1" min="5" max="5"/>
-    <col width="77" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col hidden="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col hidden="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col hidden="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col hidden="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col hidden="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col hidden="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="105" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
-    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col hidden="1" min="6" max="6"/>
+    <col width="77" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col hidden="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col hidden="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col hidden="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col hidden="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col hidden="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="105" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
     <col width="38" customWidth="1" min="28" max="28"/>
     <col width="38" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="38" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,130 +483,135 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD2" s="1" t="inlineStr">
+      <c r="AE2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -622,72 +628,72 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Knee Face Bash</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Knee Face Bash</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Can be Tech Rolled, damage remains the same.</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>b4c8ba1d-0945-4a55-946a-120783ffcbe2</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>7b11e8fd-c128-44f1-9538-bd09cd381913</t>
         </is>
@@ -704,62 +710,62 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Rib Crusher</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Rib Crusher</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>10b1c729-146d-4906-ab09-b02ffd1b780e</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>7de8afb3-ebe2-48e9-b956-1f703a52d031</t>
         </is>
@@ -783,55 +789,60 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Head Breaker</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Head Breaker</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>9b8fd4d4-3616-48c9-9abf-dc9f662f6010</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>9b8fd4d4-3616-48c9-9abf-dc9f662f6010</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -855,55 +866,60 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Face Breaker</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Face Breaker</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>14,26</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>14,26</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>ee9855c7-2c2c-4519-b9a4-792540aae26a</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>ee9855c7-2c2c-4519-b9a4-792540aae26a</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -927,55 +943,60 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Reverse Neck Toss</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Reverse Neck Toss</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>b9d85c75-dc82-4368-83a4-ec8806a63d3b</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>b9d85c75-dc82-4368-83a4-ec8806a63d3b</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1012,130 +1033,135 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H10" s="1" t="inlineStr">
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="J10" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
+      <c r="K10" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K10" s="1" t="inlineStr">
+      <c r="L10" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L10" s="1" t="inlineStr">
+      <c r="M10" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M10" s="1" t="inlineStr">
+      <c r="N10" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N10" s="1" t="inlineStr">
+      <c r="O10" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O10" s="1" t="inlineStr">
+      <c r="P10" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P10" s="1" t="inlineStr">
+      <c r="Q10" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q10" s="1" t="inlineStr">
+      <c r="R10" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R10" s="1" t="inlineStr">
+      <c r="S10" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S10" s="1" t="inlineStr">
+      <c r="T10" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T10" s="1" t="inlineStr">
+      <c r="U10" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U10" s="1" t="inlineStr">
+      <c r="V10" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V10" s="1" t="inlineStr">
+      <c r="W10" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W10" s="1" t="inlineStr">
+      <c r="X10" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X10" s="1" t="inlineStr">
+      <c r="Y10" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y10" s="1" t="inlineStr">
+      <c r="Z10" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z10" s="1" t="inlineStr">
+      <c r="AA10" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA10" s="1" t="inlineStr">
+      <c r="AB10" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB10" s="1" t="inlineStr">
+      <c r="AC10" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC10" s="1" t="inlineStr">
+      <c r="AD10" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD10" s="1" t="inlineStr">
+      <c r="AE10" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1152,82 +1178,82 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>860ca5b2-c284-48f4-bcbc-f53831f909e1</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>0fd4e2f1-d774-4d3a-a67c-569ae01061e6</t>
         </is>
@@ -1244,82 +1270,82 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>01dcae2d-2ccd-4fc6-be56-6c61b47c7754</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>39c2cfbf-32df-4920-bf43-fa01c868fed8</t>
         </is>
@@ -1336,82 +1362,82 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>5c237bdb-23b1-4bae-ba17-ec40c6b7614c</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>bd37f449-b9d6-41c5-8ba3-e7b113012c81</t>
         </is>
@@ -1428,82 +1454,82 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>9bbe53d5-1f65-4f38-86aa-a1f51977ece1</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>7adff529-b823-4daa-ab2b-c6056a9c21a4</t>
         </is>
@@ -1520,82 +1546,82 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>0fb8f52a-9c2c-4a67-8ecb-9b59d7bb0dd3</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>55227515-2296-43ac-8fb1-afdfac33b62f</t>
         </is>
@@ -1612,82 +1638,82 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>a438d352-84c8-452f-b617-d63aee0551c4</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>70ff750a-8bc6-45f6-bad6-5df73f0bc99b</t>
         </is>
@@ -1704,82 +1730,82 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>4a1ce807-f2a2-487b-9a19-e3adab1b8bbd</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>98cb33e3-7d31-48c8-915d-013ede5f1515</t>
         </is>
@@ -1796,82 +1822,82 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>85d09a3b-03e8-4ee6-919a-8db0a2bf7ec1</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>68f5f87f-de28-4669-8783-f90e41a0b310</t>
         </is>
@@ -1888,82 +1914,82 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>1327a4fd-b0e6-4037-9a67-4ef9660d8b22</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>b8a31c86-1bec-4e14-b9c8-6665686667ec</t>
         </is>
@@ -1980,82 +2006,82 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>78456db6-b3d7-4449-9313-bc6c351559c0</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>05d01bc8-97e4-4fb4-b0bb-0c4e1df5cf9e</t>
         </is>
@@ -2072,82 +2098,82 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>b05b1481-8a37-44d3-9e8a-43c7d27a8dcc</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>29b14bb1-d541-44ba-83f6-98f844185120</t>
         </is>
@@ -2164,82 +2190,82 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>bf623ce2-78cc-432b-a4ab-87534c9e135d</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>faeaa586-460d-4415-b852-ea6b4f8aa7ea</t>
         </is>
@@ -2256,82 +2282,82 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>0c0d064c-3d05-4554-8ef2-a46a21dc2c97</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>a7949f82-aa77-4510-96c5-f586a52ed0d9</t>
         </is>
@@ -2348,82 +2374,82 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>d0a5338b-dd1b-4d0c-8d67-75a1df7921bb</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>c3663efe-c177-434a-8453-a7fee5f21113</t>
         </is>
@@ -2440,82 +2466,82 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>74297438-0e3a-4324-9ad0-dcf34a6f4b0d</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>8dee40c2-0369-4085-af21-0e0c6bf284bb</t>
         </is>
@@ -2532,82 +2558,82 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>2d21652c-c77b-4d22-a460-36dd0bc588ed</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>202c1571-0363-4c68-9806-c523e15b35da</t>
         </is>
@@ -2624,82 +2650,82 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>7f3a56c5-0093-4dcd-a85e-12a0446b0e19</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>e4c51dc8-b96d-42ea-adbe-9de17daab5c6</t>
         </is>
@@ -2716,82 +2742,82 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>183601f0-b919-4353-a89a-1199faed09df</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>d1ed7c35-e7ad-45b0-af6c-bafd9fcf1788</t>
         </is>
@@ -2808,82 +2834,82 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>50042001-8cdc-4ae6-9c26-95153c23f231</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>75295ab8-5a7f-4671-8e6a-5f963c0dbfeb</t>
         </is>
@@ -2900,82 +2926,82 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>ad217960-c05e-4b3b-a009-980fe108e8f8</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>3ca50a94-daac-40bb-a4e6-63f6dd62875c</t>
         </is>
@@ -2992,82 +3018,82 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>34a22635-8be8-4874-9efd-b27086bfb357</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>011e2e18-754a-49db-8f99-7a663c3e1b00</t>
         </is>
@@ -3084,82 +3110,82 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>87e01d51-6dab-4881-8c78-b2ee3ae0ed3d</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>b4c37261-46fc-4a8d-b2e3-549dba17ec9a</t>
         </is>
@@ -3176,82 +3202,82 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>19f06a20-92d4-4e54-a8a3-948ea368475d</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>734d0680-695d-4e51-9a99-b6cfcb35a625</t>
         </is>
@@ -3268,82 +3294,82 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>115b24d0-2156-4195-9048-c535df76c89f</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>6cb840c6-bfa6-4508-9777-a7f44cad4dd3</t>
         </is>
@@ -3380,130 +3406,135 @@
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
+      <c r="H37" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H37" s="1" t="inlineStr">
+      <c r="I37" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I37" s="1" t="inlineStr">
+      <c r="J37" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J37" s="1" t="inlineStr">
+      <c r="K37" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K37" s="1" t="inlineStr">
+      <c r="L37" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L37" s="1" t="inlineStr">
+      <c r="M37" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M37" s="1" t="inlineStr">
+      <c r="N37" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N37" s="1" t="inlineStr">
+      <c r="O37" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O37" s="1" t="inlineStr">
+      <c r="P37" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P37" s="1" t="inlineStr">
+      <c r="Q37" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q37" s="1" t="inlineStr">
+      <c r="R37" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R37" s="1" t="inlineStr">
+      <c r="S37" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S37" s="1" t="inlineStr">
+      <c r="T37" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T37" s="1" t="inlineStr">
+      <c r="U37" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U37" s="1" t="inlineStr">
+      <c r="V37" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V37" s="1" t="inlineStr">
+      <c r="W37" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W37" s="1" t="inlineStr">
+      <c r="X37" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X37" s="1" t="inlineStr">
+      <c r="Y37" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y37" s="1" t="inlineStr">
+      <c r="Z37" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z37" s="1" t="inlineStr">
+      <c r="AA37" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA37" s="1" t="inlineStr">
+      <c r="AB37" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB37" s="1" t="inlineStr">
+      <c r="AC37" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC37" s="1" t="inlineStr">
+      <c r="AD37" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD37" s="1" t="inlineStr">
+      <c r="AE37" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3520,102 +3551,102 @@
           <t>df+1 ,2</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Double Face Buster</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Double Face Buster</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>-3 -2</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>-3 -2</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>+8 KD</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>+8 KD</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>+8 KD</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>+8 KD</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>13,10</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>13,10</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>a9e25f22-e542-422e-9b16-5ad7755ac569</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>c06c40d2-d97d-408d-8148-abbd2dd85346</t>
         </is>
@@ -3632,92 +3663,92 @@
           <t>1 ,2 ,1 ,2</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Bruce Rush</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Bruce Rush</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>1 1 1 1</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>+1 -4 -1 -6</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>+1 -4 -1 -6</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>+6 +12 +10 KD</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>+6 +12 +10 KD</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>+6 +12 +10 KD</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>+6 +12 +10 KD</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>10,12,12,15</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>10,12,12,15</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>hhmm</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>hhmm</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>d4314cff-7c6d-40d3-8c01-c550e5a2fac4</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>99bc7590-d62c-42fe-acb4-f2ec4644339f</t>
         </is>
@@ -3734,92 +3765,92 @@
           <t>f+1 ,2 ,1</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Triple Elbow Rush</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Triple Elbow Rush</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>-10 -10 -20</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>-10 -10 -20</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>+1 +1 KD</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>+1 +1 KD</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>+1 +1 KD</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>+1 +1 KD</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>7,10,21</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>7,10,21</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>7eaffde2-f39f-42bd-8eb3-7c7b1fda908f</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>c703f18b-b04c-49e8-8a58-632578683200</t>
         </is>
@@ -3836,97 +3867,97 @@
           <t>SS+1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Nightmare Elbow</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Nightmare Elbow</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>MS FCDc</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>9d4cff35-9b64-4582-96ab-7d7cbaf5d671</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>2142688f-17e6-4cd0-8882-39950aa13b6b</t>
         </is>
@@ -3943,97 +3974,97 @@
           <t>b+1</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Nightmare Back Knuckle</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Nightmare Back Knuckle</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>CSc</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>08162ce2-a9a9-47c0-b8f2-d0b5e4d1671e</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>c4273042-2413-4f0c-bc57-1835d33d38ba</t>
         </is>
@@ -4050,97 +4081,97 @@
           <t>FC+df,d,df+1</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Tornado Upper</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Tornado Upper</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>29fe5cae-cd9d-4770-9e25-d9a0de1584d5</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>ddb7a90d-7c85-44bb-930c-a74667415f61</t>
         </is>
@@ -4157,92 +4188,92 @@
           <t>1 ,2</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>+1 -4</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>+1 -4</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>+6 +12</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>+6 +12</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>+6 +12</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>+6 +12</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>10,12</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>10,12</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>3ebcfdda-fc9f-4a05-8aa6-9cdf3c001cef</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>41bd99c9-3b67-4502-94ef-b80ed5fecc0f</t>
         </is>
@@ -4259,92 +4290,92 @@
           <t>1 ,2 ,3</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>– Mid Spin Kick</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Double Punch – Mid Spin Kick</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>+1 -4 -6</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>+6 +12 KD</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>+6 +12 KD</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>10,12,20</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>ec89cbf8-ca5d-4a68-a1d0-2134b17ae896</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>3c984d67-918b-457f-9ddf-60d7cbef6456</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>3ebcfdda-fc9f-4a05-8aa6-9cdf3c001cef</t>
         </is>
@@ -4361,92 +4392,92 @@
           <t>1 ,2 ,4</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>– Thai Mid Kick</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Double Punch – Thai Mid Kick</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>+1 -4 -14</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>+6 +12 -3</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>+6 +12 -3</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>10,12,18</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>7ff8e931-f8b5-4fbb-9fc8-e1f4aeacfb2b</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>82a9a2b2-80b0-4c2e-91ad-bcd9df8e7f50</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>3ebcfdda-fc9f-4a05-8aa6-9cdf3c001cef</t>
         </is>
@@ -4463,92 +4494,92 @@
           <t>1 ,2 ,f+4</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>– Thai Face Kick</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Double Punch – Thai Face Kick</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>+1 -4 -15</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>+6 +12 -4</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>+6 +12 -4</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>10,12,26</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>726c40cb-b801-4194-b353-e5af75e69d00</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>54f6ae17-5a85-46ef-81dc-aecd6d780113</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>3ebcfdda-fc9f-4a05-8aa6-9cdf3c001cef</t>
         </is>
@@ -4565,92 +4596,92 @@
           <t>1 ,2 ,d+4</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>– Shin Kick</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Double Punch – Shin Kick</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>+1 -4 -18</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>+6 +12 -7</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>+6 +12 -7</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>10,12,10</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>hhl</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>deb1b940-e236-43b3-82e5-9721ff9b870c</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>9e78e4c7-2bc7-47f1-9380-adcf2442da20</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>3ebcfdda-fc9f-4a05-8aa6-9cdf3c001cef</t>
         </is>
@@ -4667,92 +4698,92 @@
           <t>1 ,2 ,d+4 &lt;3</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>–– Thai High Kick</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Double Punch – Shin Kick – Thai High Kick</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>1 1 1 1</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>+1 -4 -18 -4</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>+6 +12 -7 KD</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>+6 +12 -7 KD</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>10,12,10,25</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>hhlh</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>182bf1af-5e03-4bb6-8c42-eb9c628a1228</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>f6adb272-88cb-45f7-8fec-62c26fc2b908</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>deb1b940-e236-43b3-82e5-9721ff9b870c</t>
         </is>
@@ -4769,92 +4800,92 @@
           <t>1 ,4 ,3</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Southern Cross</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Southern Cross</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>+1 -4 -15</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>+1 -4 -15</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>+6 +5 KD</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>+6 +5 KD</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>+6 +5 KD</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>+6 +5 KD</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>10,20,17</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>10,20,17</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>446539cf-b0a0-4986-80a2-7477d8cac43f</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>5a9d1898-4f50-46b3-8c2d-2366f97cd211</t>
         </is>
@@ -4871,92 +4902,92 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Sledge Hammer</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Sledge Hammer</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>b216e870-8337-4d08-b828-e72717925487</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>a4552fab-1502-4842-9b45-8b344f029fd1</t>
         </is>
@@ -4973,52 +5004,52 @@
           <t>df+1+2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Short Step In Upper</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Short Step In Upper</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>de6652b6-9b8e-4536-8ca9-003c548760fe</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>d8c28c8a-6443-4a49-9469-7b1e1e8e6c5a</t>
         </is>
@@ -5035,92 +5066,92 @@
           <t>f+1+2</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Slice Elbow</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Slice Elbow</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>0595e1ea-5a76-4cf3-ad5b-b2fb0495eb64</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>db49a38f-486f-4180-bba8-e55d56a64764</t>
         </is>
@@ -5137,102 +5168,102 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Face Buster</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Face Buster</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>55ef5622-a1ba-4ebc-a791-cf68318d95aa</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>8d47d940-4d9e-4584-a495-deeb4f5104a1</t>
         </is>
@@ -5249,97 +5280,97 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>SH JGc</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>e332f562-a23f-4af7-b68b-67936e92dbf6</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>24ea510b-a6fd-4d47-9591-c191bd97f4b1</t>
         </is>
@@ -5356,92 +5387,92 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Right Jab</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Right Jab</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>b91b4a86-9c45-48fe-9086-f6a6af8d9d29</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
+      <c r="AC56" t="inlineStr">
         <is>
           <t>8b9cdbfe-d955-41c4-a9d8-f50bb755ec31</t>
         </is>
@@ -5458,92 +5489,92 @@
           <t>2 ,3</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>– Mid Spin Kick</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Right Jab – Mid Spin Kick</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>-4 -6</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>+12 KD</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>+12 KD</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>12,20</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>82c2b6d1-798d-415d-8b39-2edadcbbd61c</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="AC57" t="inlineStr">
         <is>
           <t>73acfec1-c78a-4590-8561-22faed4c6bf7</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
+      <c r="AD57" t="inlineStr">
         <is>
           <t>b91b4a86-9c45-48fe-9086-f6a6af8d9d29</t>
         </is>
@@ -5560,92 +5591,92 @@
           <t>2 ,4</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>– Thai Mid Kick</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Right Jab – Thai Mid Kick</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>-4 -14</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>+12 -3</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>+12 -3</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>12,18</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>18a5649c-8480-4fef-a4e7-befb0c05abbf</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>6fd24b73-5990-4db6-a1fd-0067e73d5f5f</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
+      <c r="AD58" t="inlineStr">
         <is>
           <t>b91b4a86-9c45-48fe-9086-f6a6af8d9d29</t>
         </is>
@@ -5662,92 +5693,92 @@
           <t>2 ,f+4</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>– Thai Face Kick</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Right Jab – Thai Face Kick</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>-4 -15</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>+12 -4</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>+12 -4</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>12,26</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>f40c0757-48c4-4ec4-ba26-63e19ed34c3f</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AC59" t="inlineStr">
         <is>
           <t>9b2f4477-28c8-4b45-9c55-2ffebc945029</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
+      <c r="AD59" t="inlineStr">
         <is>
           <t>b91b4a86-9c45-48fe-9086-f6a6af8d9d29</t>
         </is>
@@ -5764,92 +5795,92 @@
           <t>2 ,d+4</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>– Shin Kick</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Right Jab – Shin Kick</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>-4 -18</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>+12 -7</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>+12 -7</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>12,10</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>hl</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>6476d7a3-157d-46cd-8bc4-bfe8d1f59233</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>276f5e73-0658-4212-bfe9-764ea6c84b1f</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
+      <c r="AD60" t="inlineStr">
         <is>
           <t>b91b4a86-9c45-48fe-9086-f6a6af8d9d29</t>
         </is>
@@ -5866,92 +5897,92 @@
           <t>2 ,d+4 &lt;3</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>–– Thai High Kick</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Right Jab – Shin Kick – Thai High Kick</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>-4 -18 -4</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>+12 -7 KD</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>+12 -7 KD</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>12,10,25</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>hlh</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>a72ca988-ae9f-447b-aff5-f9b5d7402dd0</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>d6e2a4e4-d675-43d0-a660-838940ff2255</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
+      <c r="AD61" t="inlineStr">
         <is>
           <t>6476d7a3-157d-46cd-8bc4-bfe8d1f59233</t>
         </is>
@@ -5968,97 +5999,97 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Nightmare Mach Punch</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Nightmare Mach Punch</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>Reverses all punch attacks.</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>ca1218f4-ad87-492b-8cde-d99706e6db3b</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
+      <c r="AC62" t="inlineStr">
         <is>
           <t>21640777-7fe0-4821-b3dc-cdc596843a60</t>
         </is>
@@ -6075,97 +6106,97 @@
           <t>f,f+3</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Slicer</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Slicer</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>fd124a8e-8c66-4223-a19f-90ec6c519d2f</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>57e072f6-ca02-4a5b-bf8e-7dc72d8584f9</t>
         </is>
@@ -6189,95 +6220,100 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>f,f,f+3</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Sniper Slash Kick</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Sniper Slash Kick</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>59c5981c-9db7-4b24-bf94-a3bf3d693a71</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
+      <c r="AC64" t="inlineStr">
         <is>
           <t>592c7802-2465-4493-a46b-eae72ecdb105</t>
         </is>
@@ -6294,92 +6330,92 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Cyclone Edge</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Cyclone Edge</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>ecba69cb-bd51-46d8-a4ee-6c2857b16f84</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
+      <c r="AC65" t="inlineStr">
         <is>
           <t>c4e6f464-45ef-4855-a5d8-0be1302cb1e8</t>
         </is>
@@ -6396,92 +6432,92 @@
           <t>df+3 ,1</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>– Tornado Uppercut</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Cyclone Edge – Tornado Uppercut</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>-36</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>-9 -36</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>+2 KD</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>+2 KD</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>12,32</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>0401e73a-edf5-4b84-b196-6a0221dde4ad</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
+      <c r="AC66" t="inlineStr">
         <is>
           <t>b39209e2-6fb7-4ca6-a668-b2791e48c610</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
+      <c r="AD66" t="inlineStr">
         <is>
           <t>ecba69cb-bd51-46d8-a4ee-6c2857b16f84</t>
         </is>
@@ -6498,107 +6534,107 @@
           <t>3 ,2 ,1 ,4</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Bruce Gatling Special</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Bruce Gatling Special</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>1 1 1 1</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>-4 -10 -10 -7</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>-4 -10 -10 -7</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>+7 +1 KD +9</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>+7 +1 KD +9</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>+7 +1 KD +9</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>+7 +1 KD +9</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>18,11,15,12</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>18,11,15,12</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>mmml</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>mmml</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>The 3rd hit in the string juggles. You can tag of the launcher.</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>3e0f80c6-6913-49c4-bfb8-2bd7d2a9937a</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
+      <c r="AC67" t="inlineStr">
         <is>
           <t>306c8cee-ba6e-4987-a065-061ec1b75410</t>
         </is>
@@ -6615,92 +6651,92 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Thai Ankle Kick</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Thai Ankle Kick</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>33086e62-8252-4349-b26e-5168388bb653</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>9194cb71-c550-418a-bae9-3db31fbd40df</t>
         </is>
@@ -6717,92 +6753,92 @@
           <t>3 ,3</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Quick Spin Kicks</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Quick Spin Kicks</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>-4 -12</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>-4 -12</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>+7 KD</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>+7 KD</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>+7 KD</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>+7 KD</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>18,22</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>18,22</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>db5301bc-c7d5-4387-97b2-62e045da96bf</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>c195342c-928b-4d01-9fc8-ba333f57e3ff</t>
         </is>
@@ -6819,92 +6855,92 @@
           <t>b+3</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Front Kick</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Front Kick</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>7f025fb0-b5a8-417d-bcb6-97387dee9400</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>23a28bca-1f9f-4d48-abb2-d4342fa0f519</t>
         </is>
@@ -6921,97 +6957,97 @@
           <t>b+3 ,4</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>– Knee</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Front Kick – Knee</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>-6 -20</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>+5 KD</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>+5 KD</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>18,17</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>DSc</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>550666ba-faac-4038-93f0-537ad1131a33</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>c9198897-f7f6-4074-9692-32ddecb754f8</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
+      <c r="AD71" t="inlineStr">
         <is>
           <t>7f025fb0-b5a8-417d-bcb6-97387dee9400</t>
         </is>
@@ -7028,92 +7064,92 @@
           <t>b+3 ,2</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>– Right Punch</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Front Kick – Right Punch</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>-6 -4</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>+5 +7</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>+5 +7</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>18,12</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="V72" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>af4c71fa-3688-40a6-8df1-4c07c90e3d66</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
+      <c r="AC72" t="inlineStr">
         <is>
           <t>4f3153bf-e48f-4485-96c1-9f047a775c2d</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
+      <c r="AD72" t="inlineStr">
         <is>
           <t>7f025fb0-b5a8-417d-bcb6-97387dee9400</t>
         </is>
@@ -7130,52 +7166,52 @@
           <t>b,b,N+3+4</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Handspring Backflip</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Handspring Backflip</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="V73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>e2d7dac3-8a73-4a44-b785-3122f742f795</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
+      <c r="AC73" t="inlineStr">
         <is>
           <t>869319e9-76d7-4dd4-87a9-93a2a672642f</t>
         </is>
@@ -7192,92 +7228,92 @@
           <t>b,b,N+3+4 ,4</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>– Bazooka Leg</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Handspring Backflip – Bazooka Leg</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>-,15</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="V74" t="inlineStr">
         <is>
           <t>-h</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>dd304f49-3c64-4fc7-adfc-2208487d9533</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
+      <c r="AC74" t="inlineStr">
         <is>
           <t>0dc6627b-5418-4916-954d-592b8dd10fab</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
+      <c r="AD74" t="inlineStr">
         <is>
           <t>e2d7dac3-8a73-4a44-b785-3122f742f795</t>
         </is>
@@ -7294,92 +7330,92 @@
           <t>df+3+4</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Step In Mid Kick</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Step In Mid Kick</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>94ebfd30-4140-427c-9576-611e1cb33618</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
+      <c r="AC75" t="inlineStr">
         <is>
           <t>0d94e258-942d-4bdf-8536-75d237e1bdf1</t>
         </is>
@@ -7396,92 +7432,92 @@
           <t>d+3+4</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Rave Kick</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Rave Kick</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>65096705-0341-4e3a-be7b-95a426581792</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
+      <c r="AC76" t="inlineStr">
         <is>
           <t>6268bc64-26f0-4d80-b3dd-563755845491</t>
         </is>
@@ -7498,92 +7534,92 @@
           <t>d+3+4 ,3</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>– High Side Kick</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Rave Kick – High Side Kick</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>-14 -14</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>-3 -3</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>-3 -3</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>8,10</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="V77" t="inlineStr">
         <is>
           <t>lh</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>59a246c6-ff03-4929-a0ba-ec28e2f65db1</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
+      <c r="AC77" t="inlineStr">
         <is>
           <t>3abc96c6-bf86-4dc2-b9d6-56e50926cdfa</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
+      <c r="AD77" t="inlineStr">
         <is>
           <t>65096705-0341-4e3a-be7b-95a426581792</t>
         </is>
@@ -7600,102 +7636,102 @@
           <t>b,f+4</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Rising Knee</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Rising Knee</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="V78" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>e8a76de1-918e-4813-ae36-0d7fd18a9a96</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AC78" t="inlineStr">
         <is>
           <t>14d65ec8-46cd-4a44-a72a-d348c6395d5f</t>
         </is>
@@ -7712,92 +7748,92 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Chin Kick</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Chin Kick</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="V79" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>01ee3af6-5b1e-46fc-a6b0-c247b6bf4a34</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
+      <c r="AC79" t="inlineStr">
         <is>
           <t>ee3a8a51-57de-49e5-896e-ebe11e38e7e7</t>
         </is>
@@ -7814,92 +7850,92 @@
           <t>f+4 ,3 ,4</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Running Blind</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Running Blind</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>-4 -7 -11</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>-4 -7 -11</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>+7 +4 KD</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>+7 +4 KD</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>KD +4 KD</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>KD +4 KD</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>18,14,20</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>18,14,20</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>hmh</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="V80" t="inlineStr">
         <is>
           <t>hmh</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>c6f83fae-7660-4d1b-b7c8-7b92705571f5</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
+      <c r="AC80" t="inlineStr">
         <is>
           <t>5c60a8fd-898f-472f-be5d-32983010e40f</t>
         </is>
@@ -7916,97 +7952,97 @@
           <t>b+4 ,3 ,4</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Triple Knee Blast</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Triple Knee Blast</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>-5 -7 -20</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>-5 -7 -20</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>+6 +3 KD</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>+6 +3 KD</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>+6 +3 KD</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>+6 +3 KD</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>17,15,27</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>17,15,27</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="V81" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>addf9e66-d399-4547-b7bf-8aed144a525a</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
+      <c r="AC81" t="inlineStr">
         <is>
           <t>376d127d-4774-4a7c-9c64-6e2296916260</t>
         </is>
@@ -8023,92 +8059,92 @@
           <t>b+4 ,3 ,d+4</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Double Knee Blast - Ankle Kick</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Double Knee Blast - Ankle Kick</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>-5 -7 -14</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>-5 -7 -14</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>+6 +3 +2</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>+6 +3 +2</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>+6 +3 +2</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>+6 +3 +2</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>17,15,12</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>17,15,12</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>mml</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="V82" t="inlineStr">
         <is>
           <t>mml</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>eb706fd1-dd6b-42d9-ab6b-25d0086559d6</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
+      <c r="AC82" t="inlineStr">
         <is>
           <t>5b7f0548-e0d1-4c28-9d41-cd5944b29130</t>
         </is>
@@ -8125,97 +8161,97 @@
           <t>b,b+4</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Nightmare Heel Kick</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Nightmare Heel Kick</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>-27</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>-27</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="V83" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>JGc BS</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>8beef1cb-7c38-4f47-8fcb-78e8790340cb</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
+      <c r="AC83" t="inlineStr">
         <is>
           <t>944a961d-11c4-400d-afea-50663a51d303</t>
         </is>
@@ -8232,92 +8268,92 @@
           <t>SS+4 ,1</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Bull Kick - Left Hook</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Bull Kick - Left Hook</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>-13 -9</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>-13 -9</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>18,18</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>18,18</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="V84" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>bc93bb76-bae3-496d-8017-4ebcb3667f9a</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
+      <c r="AC84" t="inlineStr">
         <is>
           <t>51b2cac5-645b-4c38-9fea-046247fed821</t>
         </is>
@@ -8334,92 +8370,92 @@
           <t>SS+4 ,4</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Double Bull</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Double Bull</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>-13 -10</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>-13 -10</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>-2 KD</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>18,22</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>18,22</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="V85" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr">
+      <c r="AB85" t="inlineStr">
         <is>
           <t>02d91b18-6ede-4a7b-ae69-f965125c227a</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
+      <c r="AC85" t="inlineStr">
         <is>
           <t>1de56199-681f-42a1-9066-ae54ea83ba11</t>
         </is>
@@ -8436,92 +8472,92 @@
           <t>db+4</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Sway High Kick</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Sway High Kick</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="R86" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="V86" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA86" t="inlineStr">
+      <c r="AB86" t="inlineStr">
         <is>
           <t>c085e1c7-f904-4f8c-a3b7-ac2f10f0ec99</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
+      <c r="AC86" t="inlineStr">
         <is>
           <t>d66afd43-ef53-4d9b-bfa4-55aa2d02a535</t>
         </is>
@@ -8538,92 +8574,92 @@
           <t>f,f+4</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Bazooka Leg</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Bazooka Leg</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="U87" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="V87" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr">
+      <c r="AB87" t="inlineStr">
         <is>
           <t>ba05dd5b-ca43-4b07-8cc8-e5ece26caf21</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
+      <c r="AC87" t="inlineStr">
         <is>
           <t>98aa8b6f-20c3-4e2c-b922-914ff43a5f44</t>
         </is>
@@ -8660,130 +8696,135 @@
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F90" s="1" t="inlineStr">
+      <c r="G90" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr">
+      <c r="H90" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H90" s="1" t="inlineStr">
+      <c r="I90" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I90" s="1" t="inlineStr">
+      <c r="J90" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J90" s="1" t="inlineStr">
+      <c r="K90" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K90" s="1" t="inlineStr">
+      <c r="L90" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L90" s="1" t="inlineStr">
+      <c r="M90" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M90" s="1" t="inlineStr">
+      <c r="N90" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N90" s="1" t="inlineStr">
+      <c r="O90" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O90" s="1" t="inlineStr">
+      <c r="P90" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P90" s="1" t="inlineStr">
+      <c r="Q90" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q90" s="1" t="inlineStr">
+      <c r="R90" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R90" s="1" t="inlineStr">
+      <c r="S90" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S90" s="1" t="inlineStr">
+      <c r="T90" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T90" s="1" t="inlineStr">
+      <c r="U90" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U90" s="1" t="inlineStr">
+      <c r="V90" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V90" s="1" t="inlineStr">
+      <c r="W90" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W90" s="1" t="inlineStr">
+      <c r="X90" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X90" s="1" t="inlineStr">
+      <c r="Y90" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y90" s="1" t="inlineStr">
+      <c r="Z90" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z90" s="1" t="inlineStr">
+      <c r="AA90" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA90" s="1" t="inlineStr">
+      <c r="AB90" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB90" s="1" t="inlineStr">
+      <c r="AC90" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC90" s="1" t="inlineStr">
+      <c r="AD90" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD90" s="1" t="inlineStr">
+      <c r="AE90" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8800,82 +8841,82 @@
           <t>b+2+3</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Sidewinder</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Sidewinder</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="U91" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="V91" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="AA91" t="inlineStr">
+      <c r="AB91" t="inlineStr">
         <is>
           <t>a4b716ca-b10d-4143-b900-0474035b9c63</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
+      <c r="AC91" t="inlineStr">
         <is>
           <t>9a77e2f5-c77d-44ae-b02e-3b91333298a5</t>
         </is>
@@ -8912,130 +8953,135 @@
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F94" s="1" t="inlineStr">
+      <c r="G94" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G94" s="1" t="inlineStr">
+      <c r="H94" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H94" s="1" t="inlineStr">
+      <c r="I94" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I94" s="1" t="inlineStr">
+      <c r="J94" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J94" s="1" t="inlineStr">
+      <c r="K94" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K94" s="1" t="inlineStr">
+      <c r="L94" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L94" s="1" t="inlineStr">
+      <c r="M94" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M94" s="1" t="inlineStr">
+      <c r="N94" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N94" s="1" t="inlineStr">
+      <c r="O94" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O94" s="1" t="inlineStr">
+      <c r="P94" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P94" s="1" t="inlineStr">
+      <c r="Q94" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q94" s="1" t="inlineStr">
+      <c r="R94" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R94" s="1" t="inlineStr">
+      <c r="S94" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S94" s="1" t="inlineStr">
+      <c r="T94" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T94" s="1" t="inlineStr">
+      <c r="U94" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U94" s="1" t="inlineStr">
+      <c r="V94" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V94" s="1" t="inlineStr">
+      <c r="W94" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W94" s="1" t="inlineStr">
+      <c r="X94" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X94" s="1" t="inlineStr">
+      <c r="Y94" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y94" s="1" t="inlineStr">
+      <c r="Z94" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z94" s="1" t="inlineStr">
+      <c r="AA94" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA94" s="1" t="inlineStr">
+      <c r="AB94" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB94" s="1" t="inlineStr">
+      <c r="AC94" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC94" s="1" t="inlineStr">
+      <c r="AD94" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD94" s="1" t="inlineStr">
+      <c r="AE94" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -9052,57 +9098,57 @@
           <t>f,N,d,df+1+2+4</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Embracing Knee Strike</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Embracing Knee Strike</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="R95" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr">
+      <c r="W95" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="AA95" t="inlineStr">
+      <c r="AB95" t="inlineStr">
         <is>
           <t>2c1913ef-7e50-4413-a74d-b2910a2ebc07</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
+      <c r="AC95" t="inlineStr">
         <is>
           <t>2c1913ef-7e50-4413-a74d-b2910a2ebc07</t>
         </is>
       </c>
-      <c r="AD95" t="inlineStr">
+      <c r="AE95" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9119,57 +9165,57 @@
           <t>f,N,d,df+1+2+4 ,1+2 ,1+2 ,1+2</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>– Tumble Weed</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>Embracing Knee Strike – Tumble Weed</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>1 1 1 1</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="R96" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
+      <c r="T96" t="inlineStr">
         <is>
           <t>20,35</t>
         </is>
       </c>
-      <c r="W96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA96" t="inlineStr">
+      <c r="AB96" t="inlineStr">
         <is>
           <t>0b8f5015-6736-4b0d-9890-9ab4d0f90726</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
+      <c r="AC96" t="inlineStr">
         <is>
           <t>0b8f5015-6736-4b0d-9890-9ab4d0f90726</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
+      <c r="AD96" t="inlineStr">
         <is>
           <t>2c1913ef-7e50-4413-a74d-b2910a2ebc07</t>
         </is>
       </c>
-      <c r="AD96" t="inlineStr">
+      <c r="AE96" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9186,57 +9232,67 @@
           <t>f,N,d,df+1+2+4 ,3 ,1+2+3</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>4,1+2+3</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>f,N,d,df+1+2+4,4,1+2+3</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>– Left Knee Strike</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Embracing Knee Strike – Left Knee Strike</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="R97" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>20,15</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA97" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>1765f26e-c342-4b33-8701-d1a4207176f4</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
+      <c r="AC97" t="inlineStr">
         <is>
           <t>1765f26e-c342-4b33-8701-d1a4207176f4</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
+      <c r="AD97" t="inlineStr">
         <is>
           <t>2c1913ef-7e50-4413-a74d-b2910a2ebc07</t>
         </is>
       </c>
-      <c r="AD97" t="inlineStr">
+      <c r="AE97" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9253,62 +9309,62 @@
           <t>f,N,d,df+1+2+4 ,3 ,1+2+3 ,1 ,3 ,1+2+4</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>–– Turning Right Knee</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Embracing Knee Strike – Left Knee Strike – Turning Right Knee</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="R98" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="T98" t="inlineStr">
         <is>
           <t>20,15,25</t>
         </is>
       </c>
-      <c r="W98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>(1_2)</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>Use 1 to escape if the Left Knee Strike was done with 3, use 2 if the Left Knee Strike was done with 4.</t>
         </is>
       </c>
-      <c r="AA98" t="inlineStr">
+      <c r="AB98" t="inlineStr">
         <is>
           <t>b8fd9af3-2ecd-4885-ae0b-82af642e3380</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
+      <c r="AC98" t="inlineStr">
         <is>
           <t>b8fd9af3-2ecd-4885-ae0b-82af642e3380</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
+      <c r="AD98" t="inlineStr">
         <is>
           <t>1765f26e-c342-4b33-8701-d1a4207176f4</t>
         </is>
       </c>
-      <c r="AD98" t="inlineStr">
+      <c r="AE98" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9325,57 +9381,57 @@
           <t>f,N,d,df+1+2+4 ,3 ,1+2+3 ,1 ,3 ,1+2+4 ,2 ,4 ,1 ,1+2+3</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>––– Rising Knee</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Embracing Knee Strike – Left Knee Strike – Turning Right Knee – Rising Knee</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="R99" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="T99" t="inlineStr">
         <is>
           <t>20,15,25,40</t>
         </is>
       </c>
-      <c r="W99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AA99" t="inlineStr">
+      <c r="AB99" t="inlineStr">
         <is>
           <t>3cdc0ff6-007b-40aa-b73f-e08284f85ced</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
+      <c r="AC99" t="inlineStr">
         <is>
           <t>3cdc0ff6-007b-40aa-b73f-e08284f85ced</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
+      <c r="AD99" t="inlineStr">
         <is>
           <t>b8fd9af3-2ecd-4885-ae0b-82af642e3380</t>
         </is>
       </c>
-      <c r="AD99" t="inlineStr">
+      <c r="AE99" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9412,130 +9468,135 @@
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F102" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F102" s="1" t="inlineStr">
+      <c r="G102" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G102" s="1" t="inlineStr">
+      <c r="H102" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H102" s="1" t="inlineStr">
+      <c r="I102" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I102" s="1" t="inlineStr">
+      <c r="J102" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J102" s="1" t="inlineStr">
+      <c r="K102" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K102" s="1" t="inlineStr">
+      <c r="L102" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L102" s="1" t="inlineStr">
+      <c r="M102" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M102" s="1" t="inlineStr">
+      <c r="N102" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N102" s="1" t="inlineStr">
+      <c r="O102" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O102" s="1" t="inlineStr">
+      <c r="P102" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P102" s="1" t="inlineStr">
+      <c r="Q102" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q102" s="1" t="inlineStr">
+      <c r="R102" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R102" s="1" t="inlineStr">
+      <c r="S102" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S102" s="1" t="inlineStr">
+      <c r="T102" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T102" s="1" t="inlineStr">
+      <c r="U102" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U102" s="1" t="inlineStr">
+      <c r="V102" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V102" s="1" t="inlineStr">
+      <c r="W102" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W102" s="1" t="inlineStr">
+      <c r="X102" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X102" s="1" t="inlineStr">
+      <c r="Y102" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y102" s="1" t="inlineStr">
+      <c r="Z102" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z102" s="1" t="inlineStr">
+      <c r="AA102" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA102" s="1" t="inlineStr">
+      <c r="AB102" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB102" s="1" t="inlineStr">
+      <c r="AC102" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC102" s="1" t="inlineStr">
+      <c r="AD102" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD102" s="1" t="inlineStr">
+      <c r="AE102" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
